--- a/data/trans_dic/P25D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,69</t>
+          <t>0,77; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,66</t>
+          <t>0,27; 1,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,97</t>
+          <t>0,65; 2,95</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,24</t>
+          <t>0,44; 3,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,3</t>
+          <t>0,34; 2,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,4</t>
+          <t>0,64; 2,27</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,68</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,58</t>
+          <t>0,77; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,0</t>
+          <t>0,23; 1,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,66</t>
+          <t>0,46; 1,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,35</t>
+          <t>0,2; 1,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,26</t>
+          <t>0,4; 1,26</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,25</t>
+          <t>0,2; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,62</t>
+          <t>0,06; 0,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,94</t>
+          <t>0,17; 1,05</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,9</t>
+          <t>0,17; 1,77</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,62</t>
+          <t>0,68; 1,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,03</t>
+          <t>0,43; 0,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,13</t>
+          <t>0,62; 1,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3528; 23666</t>
+          <t>3893; 26164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1135; 7416</t>
+          <t>1220; 7795</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6036; 28266</t>
+          <t>6172; 28086</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2556; 14604</t>
+          <t>1961; 14746</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1332; 8790</t>
+          <t>1301; 9253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5170; 19984</t>
+          <t>5300; 18852</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>551; 11241</t>
+          <t>0; 11075</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1145; 9278</t>
+          <t>1274; 10727</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2334; 16707</t>
+          <t>1906; 16313</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4163; 17123</t>
+          <t>4763; 17468</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2335; 13194</t>
+          <t>1934; 12618</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7917; 25308</t>
+          <t>8062; 25249</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>969; 10652</t>
+          <t>950; 10936</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>552; 5241</t>
+          <t>523; 5146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2113; 12356</t>
+          <t>2223; 13803</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8561</t>
+          <t>0; 8085</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>743; 15667</t>
+          <t>731; 15690</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1783; 19021</t>
+          <t>1702; 17707</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22208; 54621</t>
+          <t>22806; 52272</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15409; 36636</t>
+          <t>15198; 35491</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42390; 78645</t>
+          <t>42754; 79733</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,19</t>
+          <t>0,58; 4,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,75</t>
+          <t>0,22; 1,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,95</t>
+          <t>0,62; 2,53</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,28</t>
+          <t>0,57; 3,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,42</t>
+          <t>0,37; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,27</t>
+          <t>0,72; 2,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,24; 2,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,45</t>
+          <t>0,73; 5,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,95</t>
+          <t>0,58; 2,45</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,69</t>
+          <t>0,54; 2,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,29</t>
+          <t>0,38; 1,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,26</t>
+          <t>0,5; 1,59</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,31</t>
+          <t>0,17; 2,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,61</t>
+          <t>0,09; 0,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,05</t>
+          <t>0,21; 1,08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,06</t>
+          <t>0,1; 1,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,21; 1,64</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,55</t>
+          <t>0,78; 1,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,99</t>
+          <t>0,48; 1,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,15</t>
+          <t>0,7; 1,24</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12441</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3893; 26164</t>
+          <t>3213; 23425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1220; 7795</t>
+          <t>1060; 7675</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6172; 28086</t>
+          <t>6400; 26210</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>12548</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1961; 14746</t>
+          <t>2740; 15248</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1301; 9253</t>
+          <t>1580; 9968</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5300; 18852</t>
+          <t>6500; 21639</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8181</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 11075</t>
+          <t>1132; 9970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1274; 10727</t>
+          <t>1364; 10571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1906; 16313</t>
+          <t>3838; 16107</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>19232</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4763; 17468</t>
+          <t>6106; 29013</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1934; 12618</t>
+          <t>3282; 13250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8062; 25249</t>
+          <t>9962; 31657</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6578</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>950; 10936</t>
+          <t>952; 12418</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>523; 5146</t>
+          <t>724; 6632</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2223; 13803</t>
+          <t>2898; 15130</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6783</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8085</t>
+          <t>0; 8274</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>731; 15690</t>
+          <t>814; 15113</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1702; 17707</t>
+          <t>2273; 17723</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>65763</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22806; 52272</t>
+          <t>26761; 56442</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15198; 35491</t>
+          <t>17497; 37763</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42754; 79733</t>
+          <t>49361; 87251</t>
         </is>
       </c>
     </row>
